--- a/data/2026/counties_2026.xlsx
+++ b/data/2026/counties_2026.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C45C815-B6D0-4473-981A-95C714305A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E49F63B-D723-460C-9F94-A9044305D764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Carlow</t>
   </si>
@@ -48,6 +35,9 @@
   </si>
   <si>
     <t>Donegal</t>
+  </si>
+  <si>
+    <t>Down</t>
   </si>
   <si>
     <t>Dublin</t>
@@ -132,14 +122,14 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <color rgb="FFED0000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFED0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -179,15 +169,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -523,312 +511,357 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>166</v>
+      </c>
+      <c r="C2" s="4">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>393</v>
+      </c>
+      <c r="C3" s="4">
+        <v>64</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>535</v>
+      </c>
+      <c r="C4" s="4">
+        <v>66</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2739</v>
+      </c>
+      <c r="C5" s="4">
+        <v>330</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>392</v>
+      </c>
+      <c r="C6" s="4">
+        <v>40</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>11738</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1205</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1080</v>
+      </c>
+      <c r="C9" s="4">
+        <v>167</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>658</v>
+      </c>
+      <c r="C10" s="4">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1181</v>
+      </c>
+      <c r="C11" s="4">
+        <v>155</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <v>351</v>
+      </c>
+      <c r="C12" s="4">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>195</v>
+      </c>
+      <c r="C13" s="4">
+        <v>24</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>93</v>
+      </c>
+      <c r="C14" s="4">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1195</v>
+      </c>
+      <c r="C15" s="4">
+        <v>163</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4">
+        <v>107</v>
+      </c>
+      <c r="C16" s="4">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4">
+        <v>530</v>
+      </c>
+      <c r="C17" s="4">
+        <v>39</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>320</v>
+      </c>
+      <c r="C18" s="4">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1159</v>
+      </c>
+      <c r="C19" s="4">
+        <v>103</v>
+      </c>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4">
+        <v>250</v>
+      </c>
+      <c r="C20" s="4">
+        <v>36</v>
+      </c>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4">
+        <v>411</v>
+      </c>
+      <c r="C21" s="4">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4">
+        <v>206</v>
+      </c>
+      <c r="C22" s="4">
         <v>26</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>120</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4">
+        <v>217</v>
+      </c>
+      <c r="C23" s="4">
+        <v>28</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>263</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B24" s="4">
+        <v>561</v>
+      </c>
+      <c r="C24" s="4">
+        <v>59</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4">
+        <v>752</v>
+      </c>
+      <c r="C25" s="4">
+        <v>47</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4">
+        <v>355</v>
+      </c>
+      <c r="C26" s="4">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
-        <v>400</v>
-      </c>
-      <c r="C4" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1907</v>
-      </c>
-      <c r="C5" s="4">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>271</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4">
+        <v>694</v>
+      </c>
+      <c r="C27" s="4">
+        <v>67</v>
+      </c>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4">
-        <v>8392</v>
-      </c>
-      <c r="C7" s="4">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4">
-        <v>720</v>
-      </c>
-      <c r="C8" s="4">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4">
-        <v>508</v>
-      </c>
-      <c r="C9" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4">
-        <v>816</v>
-      </c>
-      <c r="C10" s="4">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>224</v>
-      </c>
-      <c r="C11" s="4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4">
-        <v>136</v>
-      </c>
-      <c r="C12" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>66</v>
-      </c>
-      <c r="C13" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4">
-        <v>840</v>
-      </c>
-      <c r="C14" s="4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4">
-        <v>85</v>
-      </c>
-      <c r="C15" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4">
-        <v>423</v>
-      </c>
-      <c r="C16" s="4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4">
-        <v>205</v>
-      </c>
-      <c r="C17" s="4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4">
-        <v>870</v>
-      </c>
-      <c r="C18" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4">
-        <v>199</v>
-      </c>
-      <c r="C19" s="4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4">
-        <v>353</v>
-      </c>
-      <c r="C20" s="4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4">
-        <v>153</v>
-      </c>
-      <c r="C21" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4">
-        <v>137</v>
-      </c>
-      <c r="C22" s="4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4">
-        <v>417</v>
-      </c>
-      <c r="C23" s="4">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4">
-        <v>628</v>
-      </c>
-      <c r="C24" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4">
-        <v>236</v>
-      </c>
-      <c r="C25" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4">
-        <v>435</v>
-      </c>
-      <c r="C26" s="4">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4">
-        <v>240</v>
-      </c>
-      <c r="C27" s="4">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B28" s="4">
+        <v>351</v>
+      </c>
+      <c r="C28" s="4">
+        <v>60</v>
+      </c>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -836,17 +869,64 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Statistics</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">9ba6f678-e647-4dac-946a-fcabffeb8025</TermId>
+        </TermInfo>
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">#Reports</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">139e42fd-3e09-4439-bba7-8aeac7f033ff</TermId>
+        </TermInfo>
+      </Terms>
+    </m02c691f3efa402dab5cbaa8c240a9e7>
+    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Value>8</Value>
+      <Value>5</Value>
+      <Value>10</Value>
+      <Value>1</Value>
+      <Value>7</Value>
+    </TaxCatchAll>
+    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
+    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
+        </TermInfo>
+      </Terms>
+    </h1f8bb4843d6459a8b809123185593c7>
+    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </fbaa881fc4ae443f9fdafbdd527793df>
+    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">2023</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">720401db-42e9-4f5b-a7dd-0e2a6af555be</TermId>
+        </TermInfo>
+      </Terms>
+    </nb1b8a72855341e18dd75ce464e281f2>
+    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">ENT218-001-2023</eDocs_eFileName>
+    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
+        </TermInfo>
+      </Terms>
+    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="217" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="31db46a54668eb676742a70e0d207d79">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="255210a979e961074bfada2083d5f502" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1054,54 +1134,32 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </m02c691f3efa402dab5cbaa8c240a9e7>
-    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Value>5</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
-    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
-        </TermInfo>
-      </Terms>
-    </h1f8bb4843d6459a8b809123185593c7>
-    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </fbaa881fc4ae443f9fdafbdd527793df>
-    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </nb1b8a72855341e18dd75ce464e281f2>
-    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
-        </TermInfo>
-      </Terms>
-    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47D8F68B-1B72-4366-B62A-6C50E11D4CDF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67441B67-4E98-40FE-BBAD-623F4829A3CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F3C1DF0-E424-4D2B-96E3-7EDFA4CFC2A1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{063B66C0-3E81-45FD-A5CB-C38AB3AFF4EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1119,17 +1177,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4445C31A-3E1C-4C08-9E7B-4813D5B4B987}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D697EDB-83AD-4E63-942C-AE8CDD5B748B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>